--- a/PruebasFuncionalesCrearGrupoActivos.xlsx
+++ b/PruebasFuncionalesCrearGrupoActivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Megu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2D9954-A7E5-4C3E-AD24-A5DDCEF41BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A997C75-9173-44B1-B340-71EA5F562942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,19 +325,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFA4405"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFA4405"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -349,6 +336,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -359,7 +359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFA4405"/>
+        <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,20 +693,8 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
@@ -715,26 +703,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -742,56 +770,28 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyBorder="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -819,55 +819,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>277019</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image2.jpg">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="176" r="176"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="3464719" cy="1321594"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1092,7 +1043,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1759,128 +1710,128 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
     </row>
     <row r="8" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="25"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
     </row>
     <row r="12" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>46215</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>46215</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:6" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
@@ -1891,150 +1842,160 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="37"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="29" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
     </row>
     <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="29" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="41" t="s">
+      <c r="A26" s="28"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
     </row>
     <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="42" t="s">
+      <c r="A27" s="28"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="39"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="43" t="s">
+      <c r="A28" s="28"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="D25:D29"/>
+    <mergeCell ref="E25:E29"/>
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="F20:F24"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="A5:F8"/>
@@ -2045,18 +2006,8 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="D20:D24"/>
-    <mergeCell ref="E20:E24"/>
-    <mergeCell ref="F20:F24"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="B25:B29"/>
-    <mergeCell ref="D25:D29"/>
-    <mergeCell ref="E25:E29"/>
-    <mergeCell ref="F25:F29"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A20" location="'Caso 0'!A1" display="Caso 0" xr:uid="{44FEF4A2-6C19-4A50-A41F-96CD35034E76}"/>
     <hyperlink ref="A20:A24" location="'Caso 1'!A1" display="Caso 1" xr:uid="{7097B457-3028-4A75-B937-0B687D689B88}"/>
@@ -2065,8 +2016,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
